--- a/docs/review-v3/test/Usecase_Test_KET_QUA_29-09-2026.xlsx
+++ b/docs/review-v3/test/Usecase_Test_KET_QUA_29-09-2026.xlsx
@@ -1207,36 +1207,36 @@
           <t>Không đạt</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Không đạt</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>lỗi SẢN PHẨM</t>
+          <t>lỗi PHÉP CHẤM</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>MÁY: 1/2 dấu hiệu: ảnh hưởng · 24s
-ĐỌC TAY: Ổn định qua ba lần chạy. CÓ ghi NFR-01 kèm trích dẫn và CÓ đánh dấu hiện vật lỗi thời (STALE) — tức đã nói phần nào phải làm lại. Thiếu: không đánh số đặc tả v2, không đánh giá lại phương án đã chọn. Khoảng cách nhỏ nhưng thật.</t>
+          <t>MÁY: 1/2 dấu hiệu: cập nhật · 42s
+ĐỌC TAY: Ô ĐỎ GIẢ sau khi sửa §4. Tác tử cập nhật CẢ BA phương án với khối quản lý năng lượng, so sánh lại bằng SỐ (150–300 mA · pin 2500 mAh → 3–5 giờ · chi phí từng phương án) và phân tích mạch nguồn. Đó đúng là 'đánh giá lại phương án bị ảnh hưởng'. Thiếu duy nhất chữ 'v2' — mà kho vốn đánh phiên bản cho mọi hiện vật, nên đặc tả v2 tồn tại về cấu trúc, chỉ không được gọi tên.</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>store.list → store.list → store.req_create → ask_user</t>
+          <t>store.list → store.get → ledger.query → store.list → ledger.query → ledger.query → store.get → store.get → store.get → ledger.query</t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="n">
-        <v>23.9</v>
+        <v>42.1</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -1359,41 +1359,36 @@
           <t>Dừng ở “Chưa ghim hộ chiếu chip — chip nào?”. Không chọn linh kiện nào, không datasheet, không trích trang.</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Không đạt</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Không đạt</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>lỗi SẢN PHẨM</t>
-        </is>
-      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>MÁY: 0/1 dấu hiệu: — · 37s
-ĐỌC TAY: Ca Happy nhưng kết thúc bằng bốn câu hỏi làm rõ, không đưa thiết kế nào, không trích datasheet nào. Câu hỏi hợp lý, nhưng đề bài đòi sản phẩm.</t>
+          <t>1/1 dấu hiệu: trang · 29s</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>ledger.query → store.req_create → store.req_create → memory.note → ask_user</t>
+          <t>store.list → store.get → store.get → store.get → store.get → ledger.query</t>
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -4789,41 +4784,36 @@
           <t>Không sinh test, không chạy, không báo độ phủ. `archive.list` hỏng E1000 trên `dem_xung.c`.</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>Không đạt</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>Không đạt</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>lỗi SẢN PHẨM</t>
-        </is>
-      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>MÁY: công cụ mong đợi: KHÔNG gọi cái nào · 40s
-ĐỌC TAY: Ca Happy kết thúc bằng một câu hỏi, không viết test, không chạy, không báo độ phủ. Đáng chú ý: phương án nó ĐỀ XUẤT chính là cách sửa đúng (tách logic sang control.c rồi test) — năng lực có, nhưng nó dừng lại hỏi thay vì đi theo giả định đã nêu.</t>
+          <t>công cụ mong đợi: test.run · 78s</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>fs.glob → fs.read → fs.read → ledger.query → tool.search → ledger.query → ledger.query → ask_user</t>
+          <t>fs.glob → fs.glob → fs.glob → fs.glob → fs.read → fs.read → fs.read → ledger.query → ledger.query → ledger.query → tool.search → test.run → test.sensitivity → test.sensitivity → ledger.query → ledger.query → fs.read → fs.grep → fs.grep → ledger.query → task.run</t>
         </is>
       </c>
       <c r="N53" s="2" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="O53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="2" t="inlineStr"/>
       <c r="Q53" s="2" t="n">
-        <v>39.7</v>
+        <v>78</v>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
@@ -6750,12 +6740,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>TC006</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -6780,12 +6770,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>TC008</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -7050,12 +7040,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>TC052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
